--- a/data/trans_dic/IP31KM03_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM03_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,81%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>81,78; 92,11</t>
+          <t>78,92; 90,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80,11; 91,84</t>
+          <t>82,62; 92,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83,29; 90,48</t>
+          <t>82,72; 90,67</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>88,09%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>84,51; 92,27</t>
+          <t>82,18; 90,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82,65; 90,53</t>
+          <t>85,29; 92,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84,82; 90,36</t>
+          <t>85,13; 90,55</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>76,83%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>76,89; 90,09</t>
+          <t>68,4; 81,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>69,41; 81,17</t>
+          <t>72,55; 84,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74,47; 83,77</t>
+          <t>72,03; 80,83</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,99%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>73,38; 84,36</t>
+          <t>79,98; 89,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>80,13; 90,08</t>
+          <t>75,09; 85,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,95; 86,32</t>
+          <t>79,16; 85,96</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>83,79%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>82,04; 87,31</t>
+          <t>80,68; 85,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>80,89; 86,24</t>
+          <t>81,56; 86,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82,36; 86,07</t>
+          <t>82,03; 85,62</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>165</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>100286</t>
+          <t>105406</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>118634</t>
+          <t>104231</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>218920</t>
+          <t>209637</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>93439; 105236</t>
+          <t>96989; 111620</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>109596; 125648</t>
+          <t>97984; 109668</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>209108; 227161</t>
+          <t>199758; 218973</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>237</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>165855</t>
+          <t>201395</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>214844</t>
+          <t>161395</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>380699</t>
+          <t>362789</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>157281; 171735</t>
+          <t>190041; 209434</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>204565; 224071</t>
+          <t>154022; 167305</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>367802; 391824</t>
+          <t>350610; 372902</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>178</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>156011</t>
+          <t>125093</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>138481</t>
+          <t>121967</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>294494</t>
+          <t>247060</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>144744; 169601</t>
+          <t>113909; 135116</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>127079; 148605</t>
+          <t>112480; 130376</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>276551; 311083</t>
+          <t>231604; 259920</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>189</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>131351</t>
+          <t>141828</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>152095</t>
+          <t>132149</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>283446</t>
+          <t>273977</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>120717; 138786</t>
+          <t>132903; 149284</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>142080; 159715</t>
+          <t>123126; 140713</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>269868; 295052</t>
+          <t>261352; 283778</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>784</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>769</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>784</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>553504</t>
+          <t>573722</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>624054</t>
+          <t>519742</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1177558</t>
+          <t>1093463</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>535855; 570235</t>
+          <t>554146; 590560</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>602396; 642254</t>
+          <t>504214; 534529</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1151284; 1203148</t>
+          <t>1070568; 1117360</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM03_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM03_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman verduras frescas o cocinadas una vez al día (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>85,77%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>87,89%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>86,81%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>78,92; 90,83</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>82,62; 92,47</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>82,72; 90,67</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>87,09%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>89,37%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>88,09%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>82,18; 90,57</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>85,29; 92,64</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>85,13; 90,55</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>75,12%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>78,67%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>76,83%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>68,4; 81,14</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>72,55; 84,09</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>72,03; 80,83</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>85,35%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>80,59%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>82,99%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>79,98; 89,84</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>75,09; 85,81</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>79,16; 85,96</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>83,53%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>84,07%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>83,79%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>80,68; 85,98</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>81,56; 86,46</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>82,03; 85,62</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.8576847340353855</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.878859380551187</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.868083599797205</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>105406</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>104231</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>209637</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.7891996055490781</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.8261852662403463</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.8271750458904208</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>96989; 111620</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>97984; 109668</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>199758; 218973</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.9082504653285078</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.9247019905568615</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.9067448169223395</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>516</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.870932375776858</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.8936934698127736</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.880913330489711</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>201395</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>161395</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>362789</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.8218306591440946</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.8528664355373109</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.8513391525427381</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>190041; 209434</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>154022; 167305</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>350610; 372902</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.9056970624404983</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.9264180204151506</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.9054682018567347</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.7512101007579948</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.7866919333953135</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.7683174493801248</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>125093</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>121967</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>247060</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.6840460422758059</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.7255005792951643</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.720251699038495</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>113909; 135116</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>112480; 130376</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>231604; 259920</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.8113981434688559</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.8409296676969442</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.8083095078921972</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.8535362826079866</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.8058913184502339</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8298715358035489</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>141828</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>132149</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>273977</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.7998280238577025</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.7508636072252795</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.7916315116952599</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>132903; 149284</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>123126; 140713</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>261352; 283778</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.8984066044140256</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.8581177430215808</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.85955721627474</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>784</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1553</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.8353263234292188</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.8407236993244187</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.837883119632662</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>573722</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>519742</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1093463</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.8068234038599538</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.8156049540271836</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.820339059425935</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>554146; 590560</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>504214; 534529</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1070568; 1117360</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.8598411009676892</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.8646425858888755</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.856194125313137</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman verduras frescas o cocinadas una vez al día (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>140</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>105406</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>104231</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>209637</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>96989</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>97984</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>199758</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>111620</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>109668</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>218973</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>279</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>237</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>201395</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>161395</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>362789</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>190041</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>154022</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>350610</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>209434</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>167305</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>372902</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>163</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>178</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>125093</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>121967</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>247060</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>113909</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>112480</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>231604</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>135116</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>130376</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>259920</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>202</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>189</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>141828</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>132149</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>273977</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>132903</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>123126</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>261352</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>149284</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>140713</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>283778</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>784</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>769</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>573722</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>519742</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1093463</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>554146</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>504214</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1070568</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>590560</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>534529</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>1117360</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>